--- a/results/count/682_z23c-2/measurements.xlsx
+++ b/results/count/682_z23c-2/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,189 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v2-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1828.6667</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1051.1818</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>major_axis_length</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>80.6925</v>
+      </c>
+      <c r="C7" t="n">
+        <v>85.0115</v>
+      </c>
+      <c r="D7" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>minor_axis_length</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>29.7049</v>
+      </c>
+      <c r="C8" t="n">
+        <v>26.0194</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.1492</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.8348</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.7498</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9291</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>12</v>
       </c>
     </row>

--- a/results/count/682_z23c-2/measurements.xlsx
+++ b/results/count/682_z23c-2/measurements.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1828.6667</v>
+        <v>1994.9091</v>
       </c>
       <c r="C6" t="n">
-        <v>1340</v>
+        <v>1519</v>
       </c>
       <c r="D6" t="n">
-        <v>1051.1818</v>
+        <v>1026.7207</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80.6925</v>
+        <v>85.74550000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>85.0115</v>
+        <v>86.1566</v>
       </c>
       <c r="D7" t="n">
-        <v>26.48</v>
+        <v>22.5145</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.7049</v>
+        <v>30.4546</v>
       </c>
       <c r="C8" t="n">
-        <v>26.0194</v>
+        <v>26.8577</v>
       </c>
       <c r="D8" t="n">
-        <v>8.1492</v>
+        <v>8.8339</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8348</v>
+        <v>2.9668</v>
       </c>
       <c r="C9" t="n">
-        <v>2.7498</v>
+        <v>3.0363</v>
       </c>
       <c r="D9" t="n">
-        <v>0.953</v>
+        <v>0.8704</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.894</v>
+        <v>0.92</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9291</v>
+        <v>0.9442</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1183</v>
+        <v>0.0643</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8629</v>
+        <v>0.8555</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8885</v>
+        <v>0.8762</v>
       </c>
       <c r="D11" t="n">
-        <v>0.079</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,31 +1199,31 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1301</v>
+        <v>2083</v>
       </c>
       <c r="C14" t="n">
-        <v>46.2874</v>
+        <v>63.4325</v>
       </c>
       <c r="D14" t="n">
-        <v>38.709</v>
+        <v>42.3049</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1958</v>
+        <v>1.4994</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5483</v>
+        <v>0.7451</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9485</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5231</v>
+        <v>-1.2565</v>
       </c>
       <c r="I14" t="n">
-        <v>903.2782</v>
+        <v>905.1709</v>
       </c>
       <c r="J14" t="n">
-        <v>761.97</v>
+        <v>752.2055</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -1239,76 +1239,36 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>782</v>
+        <v>2782</v>
       </c>
       <c r="C15" t="n">
-        <v>42.255</v>
+        <v>91.2948</v>
       </c>
       <c r="D15" t="n">
-        <v>25.0545</v>
+        <v>39.6911</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6865</v>
+        <v>2.3001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8052</v>
+        <v>0.9005</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.8762</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0212</v>
+        <v>-1.4405</v>
       </c>
       <c r="I15" t="n">
-        <v>908.3197</v>
+        <v>919.6104</v>
       </c>
       <c r="J15" t="n">
-        <v>735.9604</v>
+        <v>300.2333</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2782</v>
-      </c>
-      <c r="C16" t="n">
-        <v>91.2948</v>
-      </c>
-      <c r="D16" t="n">
-        <v>39.6911</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2.3001</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.9005</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.8762</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-1.4405</v>
-      </c>
-      <c r="I16" t="n">
-        <v>919.6104</v>
-      </c>
-      <c r="J16" t="n">
-        <v>300.2333</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr">
         <is>
           <t>px</t>
         </is>
